--- a/workspace/hyper-tuner/fp-mapping-only/fp_mapping_only_tuning.xlsx
+++ b/workspace/hyper-tuner/fp-mapping-only/fp_mapping_only_tuning.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L17"/>
+  <dimension ref="A1:L33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -505,13 +505,13 @@
         <v>1</v>
       </c>
       <c r="J2" t="n">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="K2" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0178</v>
+        <v>3.806</v>
       </c>
     </row>
     <row r="3">
@@ -541,13 +541,13 @@
         <v>1</v>
       </c>
       <c r="J3" t="n">
-        <v>100</v>
+        <v>39</v>
       </c>
       <c r="K3" t="n">
-        <v>1</v>
+        <v>0.78</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0149</v>
+        <v>3.6523</v>
       </c>
     </row>
     <row r="4">
@@ -555,13 +555,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="C4" t="n">
         <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="E4" t="n">
         <v>0.9</v>
@@ -570,20 +570,20 @@
         <v>0.999</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1</v>
+        <v>0.01</v>
       </c>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="n">
         <v>1</v>
       </c>
       <c r="J4" t="n">
-        <v>100</v>
+        <v>38</v>
       </c>
       <c r="K4" t="n">
-        <v>1</v>
+        <v>0.76</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0174</v>
+        <v>1.0205</v>
       </c>
     </row>
     <row r="5">
@@ -597,7 +597,7 @@
         <v>3</v>
       </c>
       <c r="D5" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="E5" t="n">
         <v>0.9</v>
@@ -606,20 +606,20 @@
         <v>0.999</v>
       </c>
       <c r="G5" t="n">
-        <v>0.01</v>
+        <v>0.1</v>
       </c>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="n">
         <v>1</v>
       </c>
       <c r="J5" t="n">
-        <v>100</v>
+        <v>37</v>
       </c>
       <c r="K5" t="n">
-        <v>1</v>
+        <v>0.74</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0192</v>
+        <v>2.0473</v>
       </c>
     </row>
     <row r="6">
@@ -642,20 +642,20 @@
         <v>0.999</v>
       </c>
       <c r="G6" t="n">
-        <v>0.1</v>
+        <v>0.01</v>
       </c>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="n">
         <v>1</v>
       </c>
       <c r="J6" t="n">
-        <v>99</v>
+        <v>37</v>
       </c>
       <c r="K6" t="n">
-        <v>0.99</v>
+        <v>0.74</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1196</v>
+        <v>1.7999</v>
       </c>
     </row>
     <row r="7">
@@ -669,7 +669,7 @@
         <v>3</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="E7" t="n">
         <v>0.9</v>
@@ -685,13 +685,13 @@
         <v>1</v>
       </c>
       <c r="J7" t="n">
-        <v>99</v>
+        <v>36</v>
       </c>
       <c r="K7" t="n">
-        <v>0.99</v>
+        <v>0.72</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1184</v>
+        <v>0.8242</v>
       </c>
     </row>
     <row r="8">
@@ -714,20 +714,20 @@
         <v>0.999</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01</v>
+        <v>0.1</v>
       </c>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="n">
         <v>1</v>
       </c>
       <c r="J8" t="n">
-        <v>99</v>
+        <v>36</v>
       </c>
       <c r="K8" t="n">
-        <v>0.99</v>
+        <v>0.72</v>
       </c>
       <c r="L8" t="n">
-        <v>0.08649999999999999</v>
+        <v>1.5514</v>
       </c>
     </row>
     <row r="9">
@@ -735,13 +735,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="C9" t="n">
         <v>3</v>
       </c>
       <c r="D9" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="E9" t="n">
         <v>0.9</v>
@@ -757,13 +757,13 @@
         <v>1</v>
       </c>
       <c r="J9" t="n">
-        <v>98</v>
+        <v>35</v>
       </c>
       <c r="K9" t="n">
-        <v>0.98</v>
+        <v>0.7</v>
       </c>
       <c r="L9" t="n">
-        <v>0.08740000000000001</v>
+        <v>0.9043</v>
       </c>
     </row>
     <row r="10">
@@ -786,20 +786,20 @@
         <v>0.999</v>
       </c>
       <c r="G10" t="n">
-        <v>0.1</v>
+        <v>0.01</v>
       </c>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="n">
         <v>1</v>
       </c>
       <c r="J10" t="n">
-        <v>98</v>
+        <v>34</v>
       </c>
       <c r="K10" t="n">
-        <v>0.98</v>
+        <v>0.68</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0694</v>
+        <v>0.2996</v>
       </c>
     </row>
     <row r="11">
@@ -810,10 +810,10 @@
         <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D11" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="E11" t="n">
         <v>0.9</v>
@@ -826,16 +826,16 @@
       </c>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J11" t="n">
-        <v>98</v>
+        <v>34</v>
       </c>
       <c r="K11" t="n">
-        <v>0.98</v>
+        <v>0.68</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0689</v>
+        <v>15.5496</v>
       </c>
     </row>
     <row r="12">
@@ -849,7 +849,7 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="E12" t="n">
         <v>0.9</v>
@@ -862,16 +862,16 @@
       </c>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J12" t="n">
-        <v>97</v>
+        <v>34</v>
       </c>
       <c r="K12" t="n">
-        <v>0.97</v>
+        <v>0.68</v>
       </c>
       <c r="L12" t="n">
-        <v>0.0672</v>
+        <v>0.8258</v>
       </c>
     </row>
     <row r="13">
@@ -885,7 +885,7 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="E13" t="n">
         <v>0.9</v>
@@ -894,20 +894,20 @@
         <v>0.999</v>
       </c>
       <c r="G13" t="n">
-        <v>0.01</v>
+        <v>0.1</v>
       </c>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="n">
         <v>1</v>
       </c>
       <c r="J13" t="n">
-        <v>97</v>
+        <v>34</v>
       </c>
       <c r="K13" t="n">
-        <v>0.97</v>
+        <v>0.68</v>
       </c>
       <c r="L13" t="n">
-        <v>0.068</v>
+        <v>0.2995</v>
       </c>
     </row>
     <row r="14">
@@ -915,7 +915,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
         <v>1</v>
@@ -934,16 +934,16 @@
       </c>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J14" t="n">
-        <v>96</v>
+        <v>34</v>
       </c>
       <c r="K14" t="n">
-        <v>0.96</v>
+        <v>0.68</v>
       </c>
       <c r="L14" t="n">
-        <v>0.0844</v>
+        <v>0.8278</v>
       </c>
     </row>
     <row r="15">
@@ -951,13 +951,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="C15" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D15" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="E15" t="n">
         <v>0.9</v>
@@ -970,16 +970,16 @@
       </c>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J15" t="n">
-        <v>96</v>
+        <v>34</v>
       </c>
       <c r="K15" t="n">
-        <v>0.96</v>
+        <v>0.68</v>
       </c>
       <c r="L15" t="n">
-        <v>0.0867</v>
+        <v>15.7878</v>
       </c>
     </row>
     <row r="16">
@@ -990,7 +990,7 @@
         <v>1.5</v>
       </c>
       <c r="C16" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D16" t="n">
         <v>0.3</v>
@@ -1006,16 +1006,16 @@
       </c>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J16" t="n">
-        <v>96</v>
+        <v>33</v>
       </c>
       <c r="K16" t="n">
-        <v>0.96</v>
+        <v>0.66</v>
       </c>
       <c r="L16" t="n">
-        <v>0.09660000000000001</v>
+        <v>2.9583</v>
       </c>
     </row>
     <row r="17">
@@ -1023,7 +1023,7 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
         <v>1</v>
@@ -1038,20 +1038,596 @@
         <v>0.999</v>
       </c>
       <c r="G17" t="n">
-        <v>0.1</v>
+        <v>0.01</v>
       </c>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="n">
         <v>1</v>
       </c>
       <c r="J17" t="n">
-        <v>96</v>
+        <v>33</v>
       </c>
       <c r="K17" t="n">
-        <v>0.96</v>
+        <v>0.66</v>
       </c>
       <c r="L17" t="n">
-        <v>0.1002</v>
+        <v>0.3125</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>16</v>
+      </c>
+      <c r="B18" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="C18" t="n">
+        <v>3</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.999</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="n">
+        <v>3</v>
+      </c>
+      <c r="J18" t="n">
+        <v>33</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="L18" t="n">
+        <v>3.0264</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>17</v>
+      </c>
+      <c r="B19" t="n">
+        <v>3</v>
+      </c>
+      <c r="C19" t="n">
+        <v>1</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.999</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="n">
+        <v>1</v>
+      </c>
+      <c r="J19" t="n">
+        <v>33</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0.3101</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>18</v>
+      </c>
+      <c r="B20" t="n">
+        <v>3</v>
+      </c>
+      <c r="C20" t="n">
+        <v>1</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.999</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="n">
+        <v>3</v>
+      </c>
+      <c r="J20" t="n">
+        <v>33</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0.8722</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>19</v>
+      </c>
+      <c r="B21" t="n">
+        <v>3</v>
+      </c>
+      <c r="C21" t="n">
+        <v>1</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.999</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="n">
+        <v>3</v>
+      </c>
+      <c r="J21" t="n">
+        <v>33</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0.8677</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>20</v>
+      </c>
+      <c r="B22" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="C22" t="n">
+        <v>3</v>
+      </c>
+      <c r="D22" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.999</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="n">
+        <v>3</v>
+      </c>
+      <c r="J22" t="n">
+        <v>33</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="L22" t="n">
+        <v>15.93</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>21</v>
+      </c>
+      <c r="B23" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="C23" t="n">
+        <v>3</v>
+      </c>
+      <c r="D23" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0.999</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="n">
+        <v>3</v>
+      </c>
+      <c r="J23" t="n">
+        <v>33</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="L23" t="n">
+        <v>16.0301</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>22</v>
+      </c>
+      <c r="B24" t="n">
+        <v>3</v>
+      </c>
+      <c r="C24" t="n">
+        <v>3</v>
+      </c>
+      <c r="D24" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0.999</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="n">
+        <v>3</v>
+      </c>
+      <c r="J24" t="n">
+        <v>31</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="L24" t="n">
+        <v>22.1694</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>23</v>
+      </c>
+      <c r="B25" t="n">
+        <v>3</v>
+      </c>
+      <c r="C25" t="n">
+        <v>3</v>
+      </c>
+      <c r="D25" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0.999</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="n">
+        <v>3</v>
+      </c>
+      <c r="J25" t="n">
+        <v>31</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="L25" t="n">
+        <v>22.1129</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>24</v>
+      </c>
+      <c r="B26" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="C26" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0.999</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="n">
+        <v>3</v>
+      </c>
+      <c r="J26" t="n">
+        <v>30</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="L26" t="n">
+        <v>1.0686</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>25</v>
+      </c>
+      <c r="B27" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="C27" t="n">
+        <v>1</v>
+      </c>
+      <c r="D27" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0.999</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="n">
+        <v>3</v>
+      </c>
+      <c r="J27" t="n">
+        <v>30</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="L27" t="n">
+        <v>1.4693</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>26</v>
+      </c>
+      <c r="B28" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="C28" t="n">
+        <v>1</v>
+      </c>
+      <c r="D28" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0.999</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="n">
+        <v>1</v>
+      </c>
+      <c r="J28" t="n">
+        <v>30</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0.774</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>27</v>
+      </c>
+      <c r="B29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="C29" t="n">
+        <v>1</v>
+      </c>
+      <c r="D29" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0.999</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="n">
+        <v>3</v>
+      </c>
+      <c r="J29" t="n">
+        <v>30</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="L29" t="n">
+        <v>1.0645</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>28</v>
+      </c>
+      <c r="B30" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="C30" t="n">
+        <v>1</v>
+      </c>
+      <c r="D30" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0.999</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="n">
+        <v>1</v>
+      </c>
+      <c r="J30" t="n">
+        <v>30</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0.773</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>29</v>
+      </c>
+      <c r="B31" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="C31" t="n">
+        <v>1</v>
+      </c>
+      <c r="D31" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0.999</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="n">
+        <v>3</v>
+      </c>
+      <c r="J31" t="n">
+        <v>30</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="L31" t="n">
+        <v>1.472</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>30</v>
+      </c>
+      <c r="B32" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="C32" t="n">
+        <v>1</v>
+      </c>
+      <c r="D32" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0.999</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="n">
+        <v>1</v>
+      </c>
+      <c r="J32" t="n">
+        <v>30</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="L32" t="n">
+        <v>1.0977</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>31</v>
+      </c>
+      <c r="B33" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="C33" t="n">
+        <v>1</v>
+      </c>
+      <c r="D33" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0.999</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="n">
+        <v>1</v>
+      </c>
+      <c r="J33" t="n">
+        <v>30</v>
+      </c>
+      <c r="K33" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="L33" t="n">
+        <v>1.0827</v>
       </c>
     </row>
   </sheetData>
